--- a/data/trans_orig/Q5415-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2007</t>
+          <t>Población según si es capaz de salir a caminar en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80991</t>
+          <t>81250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88639</t>
+          <t>88648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>58037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65691</t>
+          <t>65674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1876</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5917</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6652</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6534</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69109</t>
+          <t>69024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78257</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90357</t>
+          <t>90320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>228067</t>
+          <t>227372</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>244988</t>
+          <t>245307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71150</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81755</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>304369</t>
+          <t>305502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324322</t>
+          <t>324666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>53042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72934</t>
+          <t>73204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88427</t>
+          <t>87938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>120641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139085</t>
+          <t>138853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>53655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54788</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>356663</t>
+          <t>356033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>383077</t>
+          <t>384604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359169</t>
+          <t>358009</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386981</t>
+          <t>386867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>52472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41470</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69914</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>68208</t>
+          <t>68956</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102127</t>
+          <t>103175</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>452081</t>
+          <t>450903</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>474405</t>
+          <t>473324</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>573141</t>
+          <t>573959</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>609438</t>
+          <t>608800</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1034936</t>
+          <t>1032750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1074629</t>
+          <t>1073526</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2012</t>
+          <t>Población según si es capaz de salir a caminar en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5587</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31116</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>42920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54637</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67009</t>
+          <t>67085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61887</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75277</t>
+          <t>75986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105654</t>
+          <t>106006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115921</t>
+          <t>115842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151087</t>
+          <t>151532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165725</t>
+          <t>165726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>39541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183543</t>
+          <t>184259</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>206941</t>
+          <t>208221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42790</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>55663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>233693</t>
+          <t>232519</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>259348</t>
+          <t>259821</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39433</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>85741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>98432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>128853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153723</t>
+          <t>153698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>220209</t>
+          <t>220664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248211</t>
+          <t>248450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49029</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48365</t>
+          <t>47827</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>51155</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>50887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>304236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336427</t>
+          <t>337490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307954</t>
+          <t>308756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>338693</t>
+          <t>339080</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>55047</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88849</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>75147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114301</t>
+          <t>114732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57291</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90393</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>89992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>130787</t>
+          <t>132649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>483320</t>
+          <t>483955</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514973</t>
+          <t>514056</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>575897</t>
+          <t>578365</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>621177</t>
+          <t>620314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1071313</t>
+          <t>1066900</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1123434</t>
+          <t>1124213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2016</t>
+          <t>Población según si es capaz de salir a caminar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>58132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67880</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>35636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>89478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102067</t>
+          <t>101699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45204</t>
+          <t>44460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57231</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67833</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108047</t>
+          <t>108236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117822</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>29618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141311</t>
+          <t>142877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158306</t>
+          <t>158822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178485</t>
+          <t>177647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192634</t>
+          <t>193257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76801</t>
+          <t>75019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>92459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>258330</t>
+          <t>258985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281086</t>
+          <t>281680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42340</t>
+          <t>41754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119071</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134728</t>
+          <t>135419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143702</t>
+          <t>143849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251109</t>
+          <t>250930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275617</t>
+          <t>275402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64824</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64824</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321451</t>
+          <t>319755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>356140</t>
+          <t>355479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>321451</t>
+          <t>319755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>356140</t>
+          <t>355479</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28676</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>57857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78205</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>70742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>110634</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96017</t>
+          <t>95357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>139959</t>
+          <t>138205</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>531103</t>
+          <t>531396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>555099</t>
+          <t>555910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>620177</t>
+          <t>619716</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>665583</t>
+          <t>664920</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1158357</t>
+          <t>1161738</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1211764</t>
+          <t>1215429</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2023</t>
+          <t>Población según si es capaz de salir a caminar en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>98123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104895</t>
+          <t>104912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57112</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>63333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157717</t>
+          <t>157737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166770</t>
+          <t>166865</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>490</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83489</t>
+          <t>83029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91906</t>
+          <t>91904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,82 +11708,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42691</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39191</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44879</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>83,51%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>131374</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>124732</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>135669</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>87,88%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42691</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>38983</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44848</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>131374</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>125660</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>135612</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88016</t>
+          <t>87669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97134</t>
+          <t>96992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129068</t>
+          <t>129010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141282</t>
+          <t>141404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>33712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55429</t>
+          <t>54211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>197334</t>
+          <t>196370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213901</t>
+          <t>213413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>275348</t>
+          <t>274723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322868</t>
+          <t>322704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>481512</t>
+          <t>481855</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>546022</t>
+          <t>546669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49147</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76139</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85377</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137708</t>
+          <t>138694</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156142</t>
+          <t>155990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219459</t>
+          <t>218557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>239373</t>
+          <t>238290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>40232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>40178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66866</t>
+          <t>67359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47672</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>222651</t>
+          <t>222498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>244036</t>
+          <t>245387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224177</t>
+          <t>223980</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247698</t>
+          <t>247296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27727</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>91226</t>
+          <t>88646</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57833</t>
+          <t>60055</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107201</t>
+          <t>106276</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34835</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56568</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64020</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147870</t>
+          <t>148390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>105249</t>
+          <t>106008</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>187405</t>
+          <t>187282</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>559892</t>
+          <t>560136</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>585320</t>
+          <t>584092</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>783336</t>
+          <t>784905</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>912303</t>
+          <t>923694</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1366242</t>
+          <t>1366759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1485334</t>
+          <t>1493727</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5415-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>80533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>88630</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44739</t>
+          <t>44248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58037</t>
+          <t>57705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65674</t>
+          <t>65669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59956</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69024</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78591</t>
+          <t>78228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90320</t>
+          <t>90812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227372</t>
+          <t>228586</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>245307</t>
+          <t>245306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70284</t>
+          <t>69827</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>305502</t>
+          <t>305057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324666</t>
+          <t>324658</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53042</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73204</t>
+          <t>72583</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>87456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120641</t>
+          <t>122720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138853</t>
+          <t>138863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53655</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29396</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>53387</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>356033</t>
+          <t>356641</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384604</t>
+          <t>385152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>358009</t>
+          <t>357108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386867</t>
+          <t>386305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52472</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>68956</t>
+          <t>67885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103175</t>
+          <t>103791</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450903</t>
+          <t>451449</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>473324</t>
+          <t>473238</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>573959</t>
+          <t>571277</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>608800</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1032750</t>
+          <t>1033361</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1073526</t>
+          <t>1075724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>32730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42920</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54914</t>
+          <t>55660</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67085</t>
+          <t>67092</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61680</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75986</t>
+          <t>75463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106006</t>
+          <t>106541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115842</t>
+          <t>116594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51363</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151532</t>
+          <t>151709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165726</t>
+          <t>165703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39541</t>
+          <t>38012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184259</t>
+          <t>183921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>208221</t>
+          <t>207230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55663</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>232519</t>
+          <t>234473</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>259821</t>
+          <t>258987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39433</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85741</t>
+          <t>86236</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98432</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128853</t>
+          <t>128934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153698</t>
+          <t>153397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>220664</t>
+          <t>220328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248450</t>
+          <t>247530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47827</t>
+          <t>47785</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>27052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>50705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>304236</t>
+          <t>305071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>337490</t>
+          <t>336672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308756</t>
+          <t>308680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>339080</t>
+          <t>339445</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55047</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>87061</t>
+          <t>86102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75147</t>
+          <t>74847</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114732</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56947</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91400</t>
+          <t>91181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89992</t>
+          <t>89289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>132649</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>483955</t>
+          <t>483579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514056</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>578365</t>
+          <t>576963</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>620314</t>
+          <t>621468</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1066900</t>
+          <t>1072439</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1124213</t>
+          <t>1124916</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58132</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>67879</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44460</t>
+          <t>45162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>52340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57415</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108236</t>
+          <t>107409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117815</t>
+          <t>117408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42751</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142877</t>
+          <t>143342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158822</t>
+          <t>158594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177647</t>
+          <t>178466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193257</t>
+          <t>193147</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75019</t>
+          <t>76093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92459</t>
+          <t>91849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>258985</t>
+          <t>260769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281680</t>
+          <t>281101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41754</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120386</t>
+          <t>120257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135419</t>
+          <t>135236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123300</t>
+          <t>125276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143849</t>
+          <t>143973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250930</t>
+          <t>250487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275402</t>
+          <t>275340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319755</t>
+          <t>320535</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>355479</t>
+          <t>355606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>319755</t>
+          <t>320535</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>355479</t>
+          <t>355606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>75645</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39016</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70742</t>
+          <t>70730</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110634</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95357</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>138205</t>
+          <t>139023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>531396</t>
+          <t>531107</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>555910</t>
+          <t>555383</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>619716</t>
+          <t>621505</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>664920</t>
+          <t>665018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1161738</t>
+          <t>1161354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1215429</t>
+          <t>1213680</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102207</t>
+          <t>114913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98123</t>
+          <t>110809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104912</t>
+          <t>117855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60894</t>
+          <t>69691</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63333</t>
+          <t>72567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>163101</t>
+          <t>184604</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157737</t>
+          <t>179121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166865</t>
+          <t>188656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88683</t>
+          <t>97842</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>91844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91904</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>50351</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>46557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44879</t>
+          <t>53081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>131374</t>
+          <t>148193</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124732</t>
+          <t>141790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135669</t>
+          <t>153005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93632</t>
+          <t>103598</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87669</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96992</t>
+          <t>107638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42419</t>
+          <t>45787</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>136051</t>
+          <t>149385</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129010</t>
+          <t>141153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141404</t>
+          <t>155028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154293</t>
+          <t>169846</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154293</t>
+          <t>169846</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154293</t>
+          <t>169846</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31466</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32623</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54211</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>205647</t>
+          <t>225107</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196370</t>
+          <t>215606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213413</t>
+          <t>233755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>309146</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>274723</t>
+          <t>106053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322704</t>
+          <t>117411</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>514794</t>
+          <t>337305</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>481855</t>
+          <t>325259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>546669</t>
+          <t>346749</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>33595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>26783</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27201</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,22 +13013,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>41356</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50025</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>81158</t>
+          <t>89799</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>84524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>94171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>157271</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138694</t>
+          <t>147848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155990</t>
+          <t>166801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>228567</t>
+          <t>247072</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218557</t>
+          <t>235566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238290</t>
+          <t>256932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>204700</t>
+          <t>219778</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204700</t>
+          <t>219778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204700</t>
+          <t>219778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296705</t>
+          <t>320572</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296705</t>
+          <t>320572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296705</t>
+          <t>320572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>45586</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56700</t>
+          <t>61553</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>73935</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>62216</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>52188</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67634</t>
+          <t>74465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>233906</t>
+          <t>249543</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>222498</t>
+          <t>236042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>245387</t>
+          <t>262124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>236018</t>
+          <t>251638</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>223980</t>
+          <t>237705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247296</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>67524</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88646</t>
+          <t>87714</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>95151</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60055</t>
+          <t>81647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106276</t>
+          <t>111482</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35751</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55318</t>
+          <t>58764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>113552</t>
+          <t>124780</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>108795</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>141245</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>158188</t>
+          <t>172075</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>106008</t>
+          <t>152531</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>187282</t>
+          <t>190360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>573440</t>
+          <t>633356</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>560136</t>
+          <t>620794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>584092</t>
+          <t>645346</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>836465</t>
+          <t>684840</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>784905</t>
+          <t>666432</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>923694</t>
+          <t>703565</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1409904</t>
+          <t>1318195</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1366759</t>
+          <t>1294012</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1493727</t>
+          <t>1340723</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017541</t>
+          <t>883760</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017541</t>
+          <t>883760</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017541</t>
+          <t>883760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1655593</t>
+          <t>1585422</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1655593</t>
+          <t>1585422</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1655593</t>
+          <t>1585422</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
